--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Turnados recibidos" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="hiddenSheet" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -462,28 +462,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:AR13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col hidden="1" width="10.7265625" customWidth="1" min="1" max="3"/>
-    <col width="13.54296875" customWidth="1" min="4" max="4"/>
-    <col width="16.54296875" customWidth="1" min="5" max="5"/>
-    <col width="29.08984375" customWidth="1" min="6" max="6"/>
-    <col width="22.81640625" customWidth="1" min="7" max="7"/>
-    <col width="11.54296875" customWidth="1" min="8" max="8"/>
-    <col width="4.08984375" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
+    <col width="13.5546875" customWidth="1" min="4" max="4"/>
+    <col width="16.5546875" customWidth="1" min="5" max="5"/>
+    <col width="29.109375" customWidth="1" min="6" max="6"/>
+    <col width="22.77734375" customWidth="1" min="7" max="7"/>
+    <col width="11.5546875" customWidth="1" min="8" max="8"/>
+    <col width="4.109375" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="15.54296875" customWidth="1" min="11" max="11"/>
-    <col width="6.08984375" customWidth="1" min="12" max="12"/>
-    <col width="56.81640625" customWidth="1" min="13" max="13"/>
-    <col width="8.453125" customWidth="1" min="14" max="39"/>
-    <col width="11.453125" customWidth="1" min="40" max="40"/>
+    <col width="15.5546875" customWidth="1" min="11" max="11"/>
+    <col width="6.109375" customWidth="1" min="12" max="12"/>
+    <col width="56.77734375" customWidth="1" min="13" max="13"/>
+    <col width="8.44140625" customWidth="1" min="14" max="39"/>
+    <col width="11.44140625" customWidth="1" min="40" max="40"/>
     <col width="40" customWidth="1" min="41" max="41"/>
     <col width="22" customWidth="1" min="42" max="42"/>
-    <col width="10.7265625" customWidth="1" min="43" max="57"/>
+    <col width="10.77734375" customWidth="1" min="43" max="57"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1">
+    <row r="1" ht="14.55" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>(No modificar) Oficialía de Partes</t>
@@ -695,7 +695,7 @@
       </c>
       <c r="AR1" s="4" t="n"/>
     </row>
-    <row r="2" ht="14.5" customHeight="1">
+    <row r="2" ht="14.55" customHeight="1">
       <c r="D2" t="inlineStr">
         <is>
           <t>CRT26-009493</t>
@@ -726,10 +726,8 @@
           <t>518998_telecomunicación_y_mercadotecnia_de_monterrey_s_a_de_c_v\01 EN\VE</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
+      <c r="Q2" t="n">
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -737,7 +735,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="14.5" customHeight="1">
+    <row r="3" ht="14.55" customHeight="1">
       <c r="D3" t="inlineStr">
         <is>
           <t>CRT26-009491</t>
@@ -774,7 +772,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="14.5" customHeight="1">
+    <row r="4" ht="14.55" customHeight="1">
       <c r="D4" t="inlineStr">
         <is>
           <t>CRT26-009485</t>
@@ -811,7 +809,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="14.5" customHeight="1">
+    <row r="5" ht="14.55" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>CRT26-009484</t>
@@ -848,7 +846,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="14.5" customHeight="1">
+    <row r="6" ht="14.55" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>CRT26-009553</t>
@@ -888,7 +886,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="14.5" customHeight="1">
+    <row r="7" ht="14.55" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>CRT26-009552</t>
@@ -925,7 +923,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="14.5" customHeight="1">
+    <row r="8" ht="14.55" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>CRT26-009549</t>
@@ -962,7 +960,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="14.4" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>CRT26-009909</t>
@@ -994,6 +992,152 @@
         </is>
       </c>
       <c r="AO9" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14.4" customHeight="1">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CRT26-010647</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7478</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ROSA ELENA DELGADO ALMARAZ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ROSA ELENA DELGADO ALMARAZ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>520668_rosa_elena_delgado_almaraz\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CRT26-025230</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>182510</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VALLE TV, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NARCISO VALLE CRUZ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>514855_valle_tv_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CRT26-025229</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>182509</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VALLE TV, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NARCISO VALLE CRUZ</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>514855_valle_tv_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CRT26-025797</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>RICARDO PLANCARTE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>RICARDO PLANCARTE</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>22/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
         </is>
@@ -1015,12 +1159,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="10.7265625" customWidth="1" min="1" max="26"/>
+    <col width="10.77734375" customWidth="1" min="1" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1">
+    <row r="1" ht="14.55" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ift_oficialia:HXODh50Obvk/Q3wEOIiLzQdzPFY5e2eYEOkzZ/AuI/QW6Zo7u3/xtVTlkbZGnWCj1vUMf9wTDBhHhC2En2d2Lg==:ift_oficialiaid=%28No%20modificar%29%20Oficial%c3%ada%20de%20Partes&amp;checksumLogicalName=%28No%20modificar%29%20Suma%20de%20comprobaci%c3%b3n%20de%20fila&amp;modifiedon=%28No%20modificar%29%20Fecha%20de%20modificaci%c3%b3n&amp;ift_name=Nombre&amp;ift_memovolante=Memo%2fVolante&amp;ift_solicitantepromovente=Solicitante%20Promovente&amp;ift_representantelegal=Representante%20Legal&amp;ift_asunto=Asunto&amp;ift_tipotrmite=Tipo%20Tr%c3%a1mite&amp;createdon=Fecha%20de%20creaci%c3%b3n</t>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -997,39 +997,36 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="14.4" customHeight="1">
+    <row r="10">
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRT26-010647</t>
+          <t>CRT26-025230</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>182510</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ROSA ELENA DELGADO ALMARAZ</t>
+          <t>VALLE TV, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ROSA ELENA DELGADO ALMARAZ</t>
+          <t>NARCISO VALLE CRUZ</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17/03/2026 00:00:00</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>520668_rosa_elena_delgado_almaraz\01 EN\VE</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>1</v>
+          <t>514855_valle_tv_s_a_de_c_v\01 EN\VE</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -1040,12 +1037,12 @@
     <row r="11">
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRT26-025230</t>
+          <t>CRT26-025229</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>182510</t>
+          <t>182509</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1077,33 +1074,36 @@
     <row r="12">
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRT26-025229</t>
+          <t>CRT26-010647</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>182509</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VALLE TV, S.A. DE C.V.</t>
+          <t>ROSA ELENA DELGADO ALMARAZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NARCISO VALLE CRUZ</t>
+          <t>ROSA ELENA DELGADO ALMARAZ</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/03/2026 00:00:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>514855_valle_tv_s_a_de_c_v\01 EN\VE</t>
-        </is>
+          <t>520668_rosa_elena_delgado_almaraz\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR13"/>
+  <dimension ref="A1:AR16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -1138,6 +1138,117 @@
         </is>
       </c>
       <c r="AO13" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CRT26-012559</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>164045</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CUALLI TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MARIA DE LOURDES VARGAS GARCIA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>522365_cualli_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRT26-024456</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>181793</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NUEVA RED INTERNET DE MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LINDA FABIOLA MONTOYA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>501807_nueva_red_internet_de_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CRT26-022857</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>179746</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>COMNET, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ALEJANDRO ACOSTA HERRERA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>501609_comnet_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
         </is>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR16"/>
+  <dimension ref="A1:AR111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -1146,32 +1146,27 @@
     <row r="14">
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRT26-012559</t>
+          <t>CRT26-025627</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>164045</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CUALLI TELECOMUNICACIONES, S.A. DE C.V.</t>
+          <t>MANUEL GUADALUPE NAVARRETE QUIROZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MARIA DE LOURDES VARGAS GARCIA</t>
+          <t>MANUEL GUADALUPE NAVARRETE QUIROZ</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>522365_cualli_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+          <t>19/06/2026 00:00:00</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -1183,72 +1178,3387 @@
     <row r="15">
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRT26-024456</t>
+          <t>CRT26-025610</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>181793</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NUEVA RED INTERNET DE MÉXICO, S. DE R.L. DE C.V.</t>
+          <t>JUAN ARIAS MONTIEL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LINDA FABIOLA MONTOYA MARTÍNEZ</t>
+          <t>JUANA RAMOS MONTIEL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>18/06/2026 00:00:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>501807_nueva_red_internet_de_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+          <t>517214_juan_arias_montiel\01 EN\VE</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Formato entregado en .json, .xlsx</t>
+          <t>Formato entregado en .json, .zip</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="D16" t="inlineStr">
         <is>
+          <t>CRT26-025397</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRT26-025393</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRT26-025390</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RURAL TECHNET, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CARLOS ARTURO BELLO HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>512562_rural_technet_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CRT26-025378</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CRT26-025354</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CRT26-025353</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>LEORAISY GABRIELA AMUNDARAIN SALAZAR</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LEORAISY GABRIELA AMUNDARAIN SALAZAR</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CRT26-025181</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CARLOS JAVIER HERNANDEZ GAYOSSO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CARLOS JAVIER HERNANDEZ GAYOSSO</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>16/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CRT26-025023</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ANTONIO LEDESMA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ANTONIO LEDESMA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CRT26-025020</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CARLOS MARTÍNEZ MACÍAS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CARLOS MARTINEZ.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>517796_carlos_martínez_macías\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CRT26-025018</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>LUIS EDUARDO SANCHEZ MORALES</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>LUIS EDUARDO SANCHEZ MORALES</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>15/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CRT26-024743</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MAYRA ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MAYRA ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>12/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CRT26-024684</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>181985</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PANAMSAT DE MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>JOSE LUIS MEJIA ESTRADA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>100722_panamsat_de_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRT26-024683</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRT26-024682</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>181984</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PANAMSAT DE MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>JOSE LUIS MEJIA ESTRADA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>100722_panamsat_de_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRT26-024679</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1943</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SIN REMITENTE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SIN REMITENTE</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>11/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRT26-024678</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRT26-024672</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MICHPRINT</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>JOSUE MACRIN CORIA LOPEZ</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>11/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CRT26-024544</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SANTIAGO CADENA SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SANTIAGO CADENA SANCHEZ</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CRT26-024541</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GUILLERMO GONZÁLEZ MORENO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>GUILLERMO GONZALEZ.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>10/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>518250_guillermo_gonzález_moreno\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CRT26-024533</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CRT26-024501</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>181809</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>COORDINADORA DE CARRIER'S, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DANIEL CASTAÑEDA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>517121_coordinadora_de_carrier_s_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CRT26-024456</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>181793</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NUEVA RED INTERNET DE MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>LINDA FABIOLA MONTOYA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>501807_nueva_red_internet_de_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CRT26-024447</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>181778</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>EDGAR EDUARDO ESPARZA GARAY</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>EDGAR EDUARDO ESPARZA GARAY</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>521132_edgar_eduardo_esparza_garay\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CRT26-024310</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FRANCISCO JAVIER ARREGUIN HERRERA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>FRANCISCO JAVIER ARREGUIN HERRERA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>09/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CRT26-024250</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15621</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MEGA CABLE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SERGIO DANILO PANCARDO COBOS</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>09/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>100418_mega_cable_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CRT26-024242</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>15623</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MEGA CABLE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERGIO DANILO PANCARDO COBOS</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>09/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>100418_mega_cable_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CRT26-024149</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>181514</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>RADIO FRECUENCIAS CONCESIONADAS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>FRANCISCO JAVIER TABOADA GARCÍA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>511078_radio_frecuencias_concesionadas_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CRT26-024016</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>15427</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SERVICIOS CELULARES MULTIPAIS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SELMA YULIANA GUERRERO LINARES</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>08/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>520267_servicios_celulares_multipais_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CRT26-024007</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1892</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GEORGINA SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>GEORGINA SANCHEZ.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>08/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CRT26-024006</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GEORGINA SANCHEZ</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CRT26-023998</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>GUILLERMO GONZÁLEZ MORENO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>GUILLERMO GONZALEZ.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>08/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>518250_guillermo_gonzález_moreno\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CRT26-023848</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>15321</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CRT26-023893</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1882</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CRT26-023888</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>181010</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>EDGEUNO MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>FEDERICO HERNÁNDEZ ARROYO</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>522481_edgeuno_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CRT26-023887</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>181009</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>EDGEUNO MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>FEDERICO HERNÁNDEZ ARROYO</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>522481_edgeuno_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CRT26-023587</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>180652</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>INTERCOMUNICACIONES URYME DEL VALLE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ALICIA GARDENIA URIBE RAMIREZ</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>100680_intercomunicaciones_uryme_del_valle_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CRT26-023580</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>15089</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE FRECUENCIAS SATELITALES, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO CARDENAS CASTRO</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>04/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>100747_comercializadora_de_frecuencias_satelitales_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CRT26-023358</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>180368</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>TECNOLOGÍA Y REDES DE DATOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>JOSÉ GUADALUPE CANDELAS ORTIZ</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>520537_tecnología_y_redes_de_datos_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CRT26-023338</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>180362</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>TECNOLOGÍA Y REDES DE DATOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>JOSÉ GUADALUPE CANDELAS ORTIZ</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>520537_tecnología_y_redes_de_datos_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CRT26-022939</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>14738</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>EDITH ARACELI RUIZ VIRUES</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>EDITH ARACELI RUIZ VIRUES</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>520527_edith_araceli_ruiz_virues\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AM55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CRT26-022937</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>14737</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>EDITH ARACELI RUIZ VIRUES</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>EDITH ARACELI RUIZ VIRUES</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>01/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>520527_edith_araceli_ruiz_virues\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="D57" t="inlineStr">
+        <is>
           <t>CRT26-022857</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>179746</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>COMNET, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>ALEJANDRO ACOSTA HERRERA</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>501609_comnet_s_a_de_c_v\01 EN\VE</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CRT26-022827</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>179702</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CRT26-022826</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>179701</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CRT26-022825</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>179699</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CRT26-022823</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>179697</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CRT26-022691</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>14615</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>PROVEEDORES DE SERVICIOS EN TELECOMUNICACIONES MÓVILES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>FELIPE HERRERA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>29/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>521841_proveedores_de_servicios_en_telecomunicaciones_móviles_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CRT26-022601</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>179291</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ULTRAVISIÓN, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CYNTHIA VALDEZ GÓMEZ</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>100405_ultravisión_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CRT26-022545</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>179223</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CRT26-022544</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>179222</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CRT26-022543</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>179221</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CRT26-022542</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>179220</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CRT26-022486</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>179138</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>521672_gerardo_martínez_agustín\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CRT26-022485</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>179137</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>521672_gerardo_martínez_agustín\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CRT26-022484</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>179136</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>521672_gerardo_martínez_agustín\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CRT26-022468</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>179131</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>521672_gerardo_martínez_agustín\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CRT26-022458</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>179130</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>521672_gerardo_martínez_agustín\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CRT26-022454</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>179129</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>521672_gerardo_martínez_agustín\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CRT26-022416</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>179085</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>521672_gerardo_martínez_agustín\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>CRT26-022412</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>179076</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>GERARDO MARTÍNEZ AGUSTÍN</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>521672_gerardo_martínez_agustín\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CRT26-022073</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>178633</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MTA COMUNICS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>JESSICA JAZMINE CAAMAÑO RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>522962_mta_comunics_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CRT26-022044</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>178534</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CRT26-022043</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>178533</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CRT26-022042</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>178532</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CRT26-022041</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>178531</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CRT26-022040</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>178530</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CRT26-022039</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>178529</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CRT26-022038</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>178528</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CRT26-022037</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>178527</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CRT26-022036</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>178526</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CRT26-022035</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>178525</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CRT26-022034</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>178524</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CRT26-022033</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>178523</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ISLIM TELCO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>517058_islim_telco_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CRT26-021954</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>14112</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CITRO TELECOM, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>CARLOS ARTURO BELLO HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>25/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>519626_citro_telecom_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CRT26-021950</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>14110</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SIERRA MADRE INTERNET, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CARLOS ARTURO BELLO HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>25/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>510327_sierra_madre_internet_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CRT26-021835</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>178254</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ROCKETEL, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>517944_rocketel_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CRT26-021834</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>178252</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ROCKETEL, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>517944_rocketel_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CRT26-021833</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>178251</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ROCKETEL, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>517944_rocketel_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CRT26-021825</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>13899</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CRT26-021824</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>13898</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>TELECABLE DEL NORESTE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO BRIBIESCA RAMIREZ</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>22/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>100442_telecable_del_noreste_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CRT26-021823</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>13897</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>REDES DE INFORMACIÓN Y ENTRETENIMIENTO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO BRIBIESCA RAMIREZ</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>22/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>100487_redes_de_información_y_entretenimiento_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CRT26-021822</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>13896</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>INTERCABLETV COMUNICACIONES Y SERVICIOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>HARLY JUAREZ GARCIA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>22/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>522641_intercabletv_comunicaciones_y_servicios_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CRT26-021821</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>13895</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>INTERCABLETV COMUNICACIONES Y SERVICIOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>HARLY JUAREZ GARCIA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>22/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>522641_intercabletv_comunicaciones_y_servicios_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AM98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CRT26-021819</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>13894</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TELEVISIÓN DE MONCLOVA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO BRIBIESCA RAMIREZ</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>22/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>100752_televisión_de_monclova_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AM99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CRT26-021818</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>13893</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>TELECABLE DEL NORESTE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO BRIBIESCA RAMIREZ</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>22/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>100442_telecable_del_noreste_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AM101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CRT26-021817</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>13892</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CRT26-021816</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>13891</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>HIPERCABLE DE MONCLOVA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO BRIBIESCA RAMIREZ</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>22/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>106274_hipercable_de_monclova_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AM103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CRT26-021641</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>13884</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ALEXIS DANIEL VALENCIA ALFARO</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ALEXIS DANIEL VALENCIA ALFARO</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>22/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>520126_alexis_daniel_valencia_alfaro\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CRT26-021516</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>13789</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>LUIS GUSTAVO GARCÍA GUTIÉRREZ</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>LUIS GUSTAVO GARCIA GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>21/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>527528_luis_gustavo_garcía_gutiérrez\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CRT26-021470</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>177828</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SERVNET MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>JORGE MORENO LOZA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>102912_servnet_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>CRT26-021468</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>177824</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SERVNET MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>JORGE MORENO LOZA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>102912_servnet_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>CRT26-021467</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>177822</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>SERVNET MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>JORGE MORENO LOZA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>102912_servnet_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>CRT26-021358</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>177711</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ALBERTO VILLEGAS SOTO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ALBERTO VILLEGAS SOTO</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>100033_alberto_villegas_soto\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO111" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
         </is>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -1188,7 +1188,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JUAN ARIAS MONTIEL</t>
+          <t>JUANA RAMOS MONTIEL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR111"/>
+  <dimension ref="A1:AR113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -4559,6 +4559,105 @@
         <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>15/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO113" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
         </is>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR113"/>
+  <dimension ref="A1:AR205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -471,7 +471,7 @@
     <col width="29.109375" customWidth="1" min="6" max="6"/>
     <col width="22.77734375" customWidth="1" min="7" max="7"/>
     <col width="11.5546875" customWidth="1" min="8" max="8"/>
-    <col width="4.109375" customWidth="1" min="9" max="9"/>
+    <col width="27.5546875" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="15.5546875" customWidth="1" min="11" max="11"/>
     <col width="6.109375" customWidth="1" min="12" max="12"/>
@@ -997,7 +997,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="14.4" customHeight="1">
       <c r="D10" t="inlineStr">
         <is>
           <t>CRT26-025230</t>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14.4" customHeight="1">
       <c r="D11" t="inlineStr">
         <is>
           <t>CRT26-025229</t>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="14.4" customHeight="1">
       <c r="D12" t="inlineStr">
         <is>
           <t>CRT26-010647</t>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="14.4" customHeight="1">
       <c r="D13" t="inlineStr">
         <is>
           <t>CRT26-025797</t>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="14.4" customHeight="1">
       <c r="D14" t="inlineStr">
         <is>
           <t>CRT26-025627</t>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="14.4" customHeight="1">
       <c r="D15" t="inlineStr">
         <is>
           <t>CRT26-025610</t>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="14.4" customHeight="1">
       <c r="D16" t="inlineStr">
         <is>
           <t>CRT26-025397</t>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="14.4" customHeight="1">
       <c r="D17" t="inlineStr">
         <is>
           <t>CRT26-025393</t>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="14.4" customHeight="1">
       <c r="D18" t="inlineStr">
         <is>
           <t>CRT26-025390</t>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="14.4" customHeight="1">
       <c r="D19" t="inlineStr">
         <is>
           <t>CRT26-025378</t>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="14.4" customHeight="1">
       <c r="D20" t="inlineStr">
         <is>
           <t>CRT26-025354</t>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="14.4" customHeight="1">
       <c r="D21" t="inlineStr">
         <is>
           <t>CRT26-025353</t>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="14.4" customHeight="1">
       <c r="D22" t="inlineStr">
         <is>
           <t>CRT26-025181</t>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="14.4" customHeight="1">
       <c r="D23" t="inlineStr">
         <is>
           <t>CRT26-025023</t>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="14.4" customHeight="1">
       <c r="D24" t="inlineStr">
         <is>
           <t>CRT26-025020</t>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="14.4" customHeight="1">
       <c r="D25" t="inlineStr">
         <is>
           <t>CRT26-025018</t>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="14.4" customHeight="1">
       <c r="D26" t="inlineStr">
         <is>
           <t>CRT26-024743</t>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="14.4" customHeight="1">
       <c r="D27" t="inlineStr">
         <is>
           <t>CRT26-024684</t>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="14.4" customHeight="1">
       <c r="D28" t="inlineStr">
         <is>
           <t>CRT26-024683</t>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="14.4" customHeight="1">
       <c r="D29" t="inlineStr">
         <is>
           <t>CRT26-024682</t>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="14.4" customHeight="1">
       <c r="D30" t="inlineStr">
         <is>
           <t>CRT26-024679</t>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="14.4" customHeight="1">
       <c r="D31" t="inlineStr">
         <is>
           <t>CRT26-024678</t>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="14.4" customHeight="1">
       <c r="D32" t="inlineStr">
         <is>
           <t>CRT26-024672</t>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="14.4" customHeight="1">
       <c r="D33" t="inlineStr">
         <is>
           <t>CRT26-024544</t>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="14.4" customHeight="1">
       <c r="D34" t="inlineStr">
         <is>
           <t>CRT26-024541</t>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="14.4" customHeight="1">
       <c r="D35" t="inlineStr">
         <is>
           <t>CRT26-024533</t>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="14.4" customHeight="1">
       <c r="D36" t="inlineStr">
         <is>
           <t>CRT26-024501</t>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="14.4" customHeight="1">
       <c r="D37" t="inlineStr">
         <is>
           <t>CRT26-024456</t>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="14.4" customHeight="1">
       <c r="D38" t="inlineStr">
         <is>
           <t>CRT26-024447</t>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="14.4" customHeight="1">
       <c r="D39" t="inlineStr">
         <is>
           <t>CRT26-024310</t>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="14.4" customHeight="1">
       <c r="D40" t="inlineStr">
         <is>
           <t>CRT26-024250</t>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="14.4" customHeight="1">
       <c r="D41" t="inlineStr">
         <is>
           <t>CRT26-024242</t>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="14.4" customHeight="1">
       <c r="D42" t="inlineStr">
         <is>
           <t>CRT26-024149</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="14.4" customHeight="1">
       <c r="D43" t="inlineStr">
         <is>
           <t>CRT26-024016</t>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="14.4" customHeight="1">
       <c r="D44" t="inlineStr">
         <is>
           <t>CRT26-024007</t>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="14.4" customHeight="1">
       <c r="D45" t="inlineStr">
         <is>
           <t>CRT26-024006</t>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="14.4" customHeight="1">
       <c r="D46" t="inlineStr">
         <is>
           <t>CRT26-023998</t>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="14.4" customHeight="1">
       <c r="D47" t="inlineStr">
         <is>
           <t>CRT26-023848</t>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="14.4" customHeight="1">
       <c r="D48" t="inlineStr">
         <is>
           <t>CRT26-023893</t>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="14.4" customHeight="1">
       <c r="D49" t="inlineStr">
         <is>
           <t>CRT26-023888</t>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="14.4" customHeight="1">
       <c r="D50" t="inlineStr">
         <is>
           <t>CRT26-023887</t>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="14.4" customHeight="1">
       <c r="D51" t="inlineStr">
         <is>
           <t>CRT26-023587</t>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="14.4" customHeight="1">
       <c r="D52" t="inlineStr">
         <is>
           <t>CRT26-023580</t>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="14.4" customHeight="1">
       <c r="D53" t="inlineStr">
         <is>
           <t>CRT26-023358</t>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="14.4" customHeight="1">
       <c r="D54" t="inlineStr">
         <is>
           <t>CRT26-023338</t>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="14.4" customHeight="1">
       <c r="D55" t="inlineStr">
         <is>
           <t>CRT26-022939</t>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="14.4" customHeight="1">
       <c r="D56" t="inlineStr">
         <is>
           <t>CRT26-022937</t>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="14.4" customHeight="1">
       <c r="D57" t="inlineStr">
         <is>
           <t>CRT26-022857</t>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="14.4" customHeight="1">
       <c r="D58" t="inlineStr">
         <is>
           <t>CRT26-022827</t>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="14.4" customHeight="1">
       <c r="D59" t="inlineStr">
         <is>
           <t>CRT26-022826</t>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="14.4" customHeight="1">
       <c r="D60" t="inlineStr">
         <is>
           <t>CRT26-022825</t>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="14.4" customHeight="1">
       <c r="D61" t="inlineStr">
         <is>
           <t>CRT26-022823</t>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="14.4" customHeight="1">
       <c r="D62" t="inlineStr">
         <is>
           <t>CRT26-022691</t>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="14.4" customHeight="1">
       <c r="D63" t="inlineStr">
         <is>
           <t>CRT26-022601</t>
@@ -2780,7 +2780,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="14.4" customHeight="1">
       <c r="D64" t="inlineStr">
         <is>
           <t>CRT26-022545</t>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="14.4" customHeight="1">
       <c r="D65" t="inlineStr">
         <is>
           <t>CRT26-022544</t>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="14.4" customHeight="1">
       <c r="D66" t="inlineStr">
         <is>
           <t>CRT26-022543</t>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="14.4" customHeight="1">
       <c r="D67" t="inlineStr">
         <is>
           <t>CRT26-022542</t>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="14.4" customHeight="1">
       <c r="D68" t="inlineStr">
         <is>
           <t>CRT26-022486</t>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="14.4" customHeight="1">
       <c r="D69" t="inlineStr">
         <is>
           <t>CRT26-022485</t>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="14.4" customHeight="1">
       <c r="D70" t="inlineStr">
         <is>
           <t>CRT26-022484</t>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="14.4" customHeight="1">
       <c r="D71" t="inlineStr">
         <is>
           <t>CRT26-022468</t>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="14.4" customHeight="1">
       <c r="D72" t="inlineStr">
         <is>
           <t>CRT26-022458</t>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="14.4" customHeight="1">
       <c r="D73" t="inlineStr">
         <is>
           <t>CRT26-022454</t>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="14.4" customHeight="1">
       <c r="D74" t="inlineStr">
         <is>
           <t>CRT26-022416</t>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="14.4" customHeight="1">
       <c r="D75" t="inlineStr">
         <is>
           <t>CRT26-022412</t>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="14.4" customHeight="1">
       <c r="D76" t="inlineStr">
         <is>
           <t>CRT26-022073</t>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="14.4" customHeight="1">
       <c r="D77" t="inlineStr">
         <is>
           <t>CRT26-022044</t>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="14.4" customHeight="1">
       <c r="D78" t="inlineStr">
         <is>
           <t>CRT26-022043</t>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="14.4" customHeight="1">
       <c r="D79" t="inlineStr">
         <is>
           <t>CRT26-022042</t>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="14.4" customHeight="1">
       <c r="D80" t="inlineStr">
         <is>
           <t>CRT26-022041</t>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="14.4" customHeight="1">
       <c r="D81" t="inlineStr">
         <is>
           <t>CRT26-022040</t>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="14.4" customHeight="1">
       <c r="D82" t="inlineStr">
         <is>
           <t>CRT26-022039</t>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="14.4" customHeight="1">
       <c r="D83" t="inlineStr">
         <is>
           <t>CRT26-022038</t>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="14.4" customHeight="1">
       <c r="D84" t="inlineStr">
         <is>
           <t>CRT26-022037</t>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="14.4" customHeight="1">
       <c r="D85" t="inlineStr">
         <is>
           <t>CRT26-022036</t>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="14.4" customHeight="1">
       <c r="D86" t="inlineStr">
         <is>
           <t>CRT26-022035</t>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="14.4" customHeight="1">
       <c r="D87" t="inlineStr">
         <is>
           <t>CRT26-022034</t>
@@ -3668,7 +3668,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="14.4" customHeight="1">
       <c r="D88" t="inlineStr">
         <is>
           <t>CRT26-022033</t>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="14.4" customHeight="1">
       <c r="D89" t="inlineStr">
         <is>
           <t>CRT26-021954</t>
@@ -3745,7 +3745,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="14.4" customHeight="1">
       <c r="D90" t="inlineStr">
         <is>
           <t>CRT26-021950</t>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="14.4" customHeight="1">
       <c r="D91" t="inlineStr">
         <is>
           <t>CRT26-021835</t>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="14.4" customHeight="1">
       <c r="D92" t="inlineStr">
         <is>
           <t>CRT26-021834</t>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="14.4" customHeight="1">
       <c r="D93" t="inlineStr">
         <is>
           <t>CRT26-021833</t>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="14.4" customHeight="1">
       <c r="D94" t="inlineStr">
         <is>
           <t>CRT26-021825</t>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="14.4" customHeight="1">
       <c r="D95" t="inlineStr">
         <is>
           <t>CRT26-021824</t>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="14.4" customHeight="1">
       <c r="D96" t="inlineStr">
         <is>
           <t>CRT26-021823</t>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="14.4" customHeight="1">
       <c r="D97" t="inlineStr">
         <is>
           <t>CRT26-021822</t>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="14.4" customHeight="1">
       <c r="D98" t="inlineStr">
         <is>
           <t>CRT26-021821</t>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="14.4" customHeight="1">
       <c r="D99" t="inlineStr">
         <is>
           <t>CRT26-021819</t>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="14.4" customHeight="1">
       <c r="D100" t="inlineStr">
         <is>
           <t>CRT26-021820</t>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="14.4" customHeight="1">
       <c r="D101" t="inlineStr">
         <is>
           <t>CRT26-021818</t>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="14.4" customHeight="1">
       <c r="D102" t="inlineStr">
         <is>
           <t>CRT26-021817</t>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="14.4" customHeight="1">
       <c r="D103" t="inlineStr">
         <is>
           <t>CRT26-021816</t>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="14.4" customHeight="1">
       <c r="D104" t="inlineStr">
         <is>
           <t>CRT26-021815</t>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="14.4" customHeight="1">
       <c r="D105" t="inlineStr">
         <is>
           <t>CRT26-021732</t>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="14.4" customHeight="1">
       <c r="D106" t="inlineStr">
         <is>
           <t>CRT26-021641</t>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="14.4" customHeight="1">
       <c r="D107" t="inlineStr">
         <is>
           <t>CRT26-021516</t>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="14.4" customHeight="1">
       <c r="D108" t="inlineStr">
         <is>
           <t>CRT26-021470</t>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="14.4" customHeight="1">
       <c r="D109" t="inlineStr">
         <is>
           <t>CRT26-021468</t>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="14.4" customHeight="1">
       <c r="D110" t="inlineStr">
         <is>
           <t>CRT26-021467</t>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="14.4" customHeight="1">
       <c r="D111" t="inlineStr">
         <is>
           <t>CRT26-021358</t>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="14.4" customHeight="1">
       <c r="D112" t="inlineStr">
         <is>
           <t>CRT26-020606</t>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="14.4" customHeight="1">
       <c r="D113" t="inlineStr">
         <is>
           <t>CRT26-002483</t>
@@ -4660,6 +4660,3673 @@
       <c r="AO113" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="14.4" customHeight="1">
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CRT26-020350</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>176455</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>COMUNICACIONES Y ENLACES DIGITALES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>LUIS ANDRÉS MONROY VALLES</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>521670_comunicaciones_y_enlaces_digitales_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="14.4" customHeight="1">
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CRT26-020277</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>12910</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MEXICO RED DE TELECOMUNICACIONES S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>FRANCISCO HERNANDEZ CHAVEZ</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>13/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="14.4" customHeight="1">
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CRT26-020281</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>12908</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>CABLEVISION, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>FRANCISCO HERNANDEZ CHAVEZ</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>13/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="R116" t="n">
+        <v>1</v>
+      </c>
+      <c r="W116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="14.4" customHeight="1">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CRT26-020279</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>12909</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>CABLEMAS TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>FRANCISCO HERNANDEZ CHAVEZ</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>13/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="14.4" customHeight="1">
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CRT26-020275</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>12911</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>OPERBES S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>FRANCISCO HERNANDEZ CHAVEZ</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>13/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="14.4" customHeight="1">
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CRT26-020271</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>12912</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>TELEVISION INTERNACIONAL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>FRANCISCO HERNANDEZ CHAVEZ</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>13/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1</v>
+      </c>
+      <c r="W119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="14.4" customHeight="1">
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CRT26-020255</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>176322</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ROGELIO VARGAS LORANCA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>ROGELIO VARGAS LORANCA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>520724_rogelio_vargas_loranca\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="14.4" customHeight="1">
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CRT26-020251</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>176321</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ROGELIO VARGAS LORANCA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ROGELIO VARGAS LORANCA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>520724_rogelio_vargas_loranca\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="14.4" customHeight="1">
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CRT26-020246</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>176318</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ROGELIO VARGAS LORANCA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ROGELIO VARGAS LORANCA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>520724_rogelio_vargas_loranca\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="14.4" customHeight="1">
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CRT26-020239</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>176310</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SES MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>MARÍA FERNANDA PALACIOS MEDINA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>100737_ses_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="14.4" customHeight="1">
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CRT26-020203</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>12883</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NEXT TELEKOM, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>MIRIAM RIVERA OLVERA</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>13/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>107341_next_telekom_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="T124" t="n">
+        <v>1</v>
+      </c>
+      <c r="V124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="14.4" customHeight="1">
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CRT26-020102</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>176195</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>WAL-MART INNOVACIÓN, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>DIEGO ALBERTO RIVERA HERNÁNDEZ</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>518782_wal_mart_innovación_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="14.4" customHeight="1">
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>CRT26-020095</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>176178</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>RED NACIONAL ÚLTIMA MILLA, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ALEJANDRO LUIS PADILLA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>518612_red_nacional_última_milla_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="14.4" customHeight="1">
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CRT26-020087</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>176162</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>LIBERTY NETWORKS SOLUTIONS MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>FEDERICO HERNÁNDEZ ARROYO</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>517078_liberty_networks_solutions_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="14.4" customHeight="1">
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>CRT26-020086</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>176144</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>MEGACABLE COMUNICACIONES DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>RAMÓN OLIVARES CHÁVEZ</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>100809_megacable_comunicaciones_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="14.4" customHeight="1">
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CRT26-020085</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>176143</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>MEGA CABLE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>RAMÓN OLIVARES CHÁVEZ</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>100418_mega_cable_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="14.4" customHeight="1">
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CRT26-020083</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>176141</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SERVICIO Y EQUIPO EN TELEFONÍA INTERNET Y TV, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>RAMÓN OLIVARES CHÁVEZ</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>105695_servicio_y_equipo_en_telefonía_internet_y_tv_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="14.4" customHeight="1">
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CRT26-020071</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>176110</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>COORDINADORA DE CARRIER'S, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>DANIEL CASTAÑEDA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>517121_coordinadora_de_carrier_s_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="14.4" customHeight="1">
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>CRT26-020061</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>12793</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN DE RADIO Y TELEVISIÓN DEL NORTE DE MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ALFONSO LUA REYES</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>100770_corporación_de_radio_y_televisión_del_norte_de_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="14.4" customHeight="1">
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CRT26-020048</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>12773</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>AT&amp;T COMERCIALIZACION MOVIL, S. DE R.L. DE C.V.; AT&amp;T COMUNICACIONES DIGITALES, S. DE R.L. DE C.V. Y GRUPO AT&amp;T CELULLAR, S. DE R.L. DE C,V,</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>CARLOS EDGARDO HIRSCH GANIEVICH</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="14.4" customHeight="1">
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CRT26-020046</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>12771</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>AT&amp;T COMERCIALIZACION MOVIL, S. DE R.L. DE C.V.; AT&amp;T COMUNICACIONES DIGITALES, S. DE R.L. DE C.V. Y GRUPO AT&amp;T CELULLAR, S. DE R.L. DE C,V,</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>CARLOS EDGARDO HIRSCH GANIEVICH</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="14.4" customHeight="1">
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CRT26-020045</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>12772</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>AT&amp;T COMERCIALIZACION MOVIL, S. DE R.L. DE C.V.; AT&amp;T COMUNICACIONES DIGITALES, S. DE R.L. DE C.V. Y GRUPO AT&amp;T CELULLAR, S. DE R.L. DE C,V,</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>CARLOS EDGARDO HIRSCH GANIEVICH</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="14.4" customHeight="1">
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CRT26-020043</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>12770</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>AT&amp;T COMERCIALIZACION MOVIL, S. DE R.L. DE C.V.; AT&amp;T COMUNICACIONES DIGITALES, S. DE R.L. DE C.V. Y GRUPO AT&amp;T CELULLAR, S. DE R.L. DE C,V,</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>CARLOS EDGARDO HIRSCH GANIEVICH</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="X136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="14.4" customHeight="1">
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CRT26-020042</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>12768</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>AT&amp;T COMERCIALIZACION MOVIL, S. DE R.L. DE C.V.; AT&amp;T COMUNICACIONES DIGITALES, S. DE R.L. DE C.V. Y GRUPO AT&amp;T CELULLAR, S. DE R.L. DE C,V,</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>CARLOS EDGARDO HIRSCH GANIEVICH</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="14.4" customHeight="1">
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CRT26-020039</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>12769</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>AT&amp;T COMERCIALIZACION MOVIL, S. DE R.L. DE C.V.; AT&amp;T COMUNICACIONES DIGITALES, S. DE R.L. DE C.V. Y GRUPO AT&amp;T CELULLAR, S. DE R.L. DE C,V,</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>CARLOS EDGARDO HIRSCH GANIEVICH</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="14.4" customHeight="1">
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CRT26-020036</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>12757</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>IP MATRIX, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>IVAN RUIZ MORENO</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>100622_ip_matrix_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="14.4" customHeight="1">
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>CRT26-020031</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>12758</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>FLO HOLDING FIBRA MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>IVAN RUIZ MORENO</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>516941_flo_holding_fibra_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="14.4" customHeight="1">
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CRT26-020030</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>176091</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>AURA ELENA GUERRERO JIMÉNEZ</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>IVÁN GUILLERMO GARIBAY GUZMÁN</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>100069_aura_elena_guerrero_jiménez\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AM141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="14.4" customHeight="1">
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CRT26-020017</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>176088</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>JOB ARTURO MORALES DURÁN</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>JOB ARTURO MORALES DURÁN</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>517753_job_arturo_morales_durán\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="14.4" customHeight="1">
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CRT26-020016</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>176087</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JOB ARTURO MORALES DURÁN</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>JOB ARTURO MORALES DURÁN</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>517753_job_arturo_morales_durán\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="14.4" customHeight="1">
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CRT26-020008</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>12745</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>STARLINK SATELLITE SYSTEMS MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>JANETH GIORDANO SERNA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>519564_starlink_satellite_systems_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="14.4" customHeight="1">
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CRT26-019978</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>12731</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>TELEFONOS DEL NOROESTE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>DANIEL ANDRES BERNAL SALAZAR</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1</v>
+      </c>
+      <c r="U145" t="n">
+        <v>1</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="14.4" customHeight="1">
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CRT26-019977</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>12730</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>TELEFONOS DE MEXICO, S.A.B. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>DANIEL ANDRES BERNAL SALAZAR</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>12/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>1</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="U146" t="n">
+        <v>1</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="14.4" customHeight="1">
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CRT26-019940</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>175953</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>FREEDOMPOP MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>JORGE ABRAHAM ÁLVAREZ GUERRERO</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>509193_freedompop_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Y147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="14.4" customHeight="1">
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CRT26-019939</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>175949</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>FREEDOMPOP MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>JORGE ABRAHAM ÁLVAREZ GUERRERO</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>509193_freedompop_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="T148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="14.4" customHeight="1">
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>CRT26-019938</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>175945</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>FREEDOMPOP MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>JORGE ABRAHAM ÁLVAREZ GUERRERO</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>509193_freedompop_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="14.4" customHeight="1">
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CRT26-019922</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>175905</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>TELECOMUNICACIONES 360, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>JESÚS MORALES AGUILAR</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>102273_telecomunicaciones_360_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="14.4" customHeight="1">
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>CRT26-019920</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>12709</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>TOTAL PLAY TELECOMUNICACIONES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>DAVID TORRES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>11/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>100467_total_play_telecomunicaciones_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AF151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="14.4" customHeight="1">
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CRT26-019915</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>12708</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>TOTAL PLAY TELECOMUNICACIONES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DAVID TORRES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>11/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>100467_total_play_telecomunicaciones_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AB152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="14.4" customHeight="1">
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CRT26-019914</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>12707</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>TOTAL PLAY TELECOMUNICACIONES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>DAVID TORRES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>11/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>100467_total_play_telecomunicaciones_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="14.4" customHeight="1">
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>CRT26-019912</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>12705</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>TOTAL PLAY TELECOMUNICACIONES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>DAVID TORRES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>11/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>100467_total_play_telecomunicaciones_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="R154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="14.4" customHeight="1">
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CRT26-019913</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>TOTAL PLAY TELECOMUNICACIONES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>DAVID TORRES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>11/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>100467_total_play_telecomunicaciones_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="W155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="14.4" customHeight="1">
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CRT26-019910</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>12704</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>TOTAL PLAY TELECOMUNICACIONES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>DAVID TORRES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>11/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>100467_total_play_telecomunicaciones_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="14.4" customHeight="1">
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CRT26-019885</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>175878</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>GUILLERMO ROBLES RAMÍREZ</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>GUILLERMO ROBLES RAMÍREZ</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>516765_guillermo_robles_ramírez\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="14.4" customHeight="1">
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CRT26-019884</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>175877</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>GUILLERMO ROBLES RAMÍREZ</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>GUILLERMO ROBLES RAMÍREZ</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>516765_guillermo_robles_ramírez\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="14.4" customHeight="1">
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>CRT26-019882</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>175876</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>GUILLERMO ROBLES RAMÍREZ</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>GUILLERMO ROBLES RAMÍREZ</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>516765_guillermo_robles_ramírez\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="14.4" customHeight="1">
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CRT26-019802</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>GRUPO MARVER, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>OSCAR REYES ROSAS</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>100453_grupo_marver_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="14.4" customHeight="1">
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CRT26-019701</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>12541</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>EURONET TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SANCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>08/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>521054_euronet_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="14.4" customHeight="1">
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CRT26-019699</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>12540</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>EURONET TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SANCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>08/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>521054_euronet_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="14.4" customHeight="1">
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CRT26-019695</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>12539</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>EURONET TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SANCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>08/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>521054_euronet_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="14.4" customHeight="1">
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CRT26-019690</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>12538</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>EURONET TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SANCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>08/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>521054_euronet_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="14.4" customHeight="1">
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CRT26-019688</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>12553</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>MARKETING 358, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>BLANCA FLOR ZAPATA ALVARADO</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>08/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>519363_marketing_358_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>1</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="14.4" customHeight="1">
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CRT26-019687</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>12554</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>BROCOMUNICACIONES MOVILES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>LYDIA DANIELA ORTIZ CENOBIO</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>08/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>519422_brocomunicaciones_moviles_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="14.4" customHeight="1">
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CRT26-019686</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>175539</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="14.4" customHeight="1">
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CRT26-019684</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>175536</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="14.4" customHeight="1">
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CRT26-019682</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>175535</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="14.4" customHeight="1">
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CRT26-019681</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>175530</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="14.4" customHeight="1">
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CRT26-019678</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>175529</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="14.4" customHeight="1">
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CRT26-019676</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>175528</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="14.4" customHeight="1">
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CRT26-019673</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>175527</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="14.4" customHeight="1">
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CRT26-019671</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>175526</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="14.4" customHeight="1">
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CRT26-019670</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>175525</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>MIGUEL AMADO ESCOBAR</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>517860_miguel_amado_escobar\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="14.4" customHeight="1">
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CRT26-019657</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>175514</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>MVS NET, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO CÁRDENAS CASTRO</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>107351_mvs_net_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="14.4" customHeight="1">
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CRT26-019654</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>175511</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE FRECUENCIAS SATELITALES, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO CÁRDENAS CASTRO</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>100747_comercializadora_de_frecuencias_satelitales_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="14.4" customHeight="1">
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CRT26-019649</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>175507</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>SATÉLITES MEXICANOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>HECTOR MANUEL FORTIS SANCHEZ</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>100649_satélites_mexicanos_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="14.4" customHeight="1">
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CRT26-019639</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>12522</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>CABLE DEL VALLE DE TOLUCA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>JUAN DANIEL AMILPAS GARCIA</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>08/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>100719_cable_del_valle_de_toluca_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>1</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="14.4" customHeight="1">
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CRT26-019570</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1597</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICA, GEOGRAFIA E INFORMATICA</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>LUIS ALBERTO TIJERINA VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>07/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="14.4" customHeight="1">
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CRT26-019560</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>AMAZON KUIPER MÉXICO, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>ERICK CAMARENA</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>07/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>520452_amazon_kuiper_méxico_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="14.4" customHeight="1">
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CRT26-019556</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>1593</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ERICK CAMARENA</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>ERICK CAMARENA</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>07/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="14.4" customHeight="1">
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CRT26-019413</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>175217</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>QUETZSAT, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>MARÍA FERNANDA PALACIOS MEDINA</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>100657_quetzsat_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="14.4" customHeight="1">
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CRT26-019357</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>175153</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>4 PLAY TELECOM, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>103021_4_play_telecom_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="14.4" customHeight="1">
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CRT26-019356</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>175152</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ARELION MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>MARÍA FERNANDA PALACIOS MEDINA</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>517066_arelion_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="14.4" customHeight="1">
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CRT26-019352</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>175146</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>IRIDIUM COMUNICACIONES DE MÉXICO, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>ROGELIO ESPINOSA CANTELLANO</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>100735_iridium_comunicaciones_de_méxico_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="14.4" customHeight="1">
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CRT26-019336</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>12343</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>WISP TINAJAS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>ERICSAEL SALGADO ROBLES</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>06/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>527146_wisp_tinajas_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="14.4" customHeight="1">
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CRT26-019330</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>IBO CELL, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>FRANCISCO ESTEBAN BUNT BUNT</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>06/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>106835_ibo_cell_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>1</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="14.4" customHeight="1">
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CRT26-019328</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>12291</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>EDILAR, S.A. DE  C.V.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>ANA LILIA ESTRELLA MONTOYA</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>06/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>517149_edilar_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>1</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="14.4" customHeight="1">
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CRT26-019327</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>12290</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>TELMOV MOVIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>RAUL ALVAREZ OSORIO</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>06/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>519208_telmov_movil_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>1</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="14.4" customHeight="1">
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CRT26-019270</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>12286</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>WIMOTELECOM, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>LYDIA DANIELA ORTIZ CENOBIO</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>06/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>518633_wimotelecom_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>1</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="14.4" customHeight="1">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CRT26-019269</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>12285</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>CELMAX MÓVIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>LYDIA DANIELA ORTIZ CENOBIO</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>517038_celmax_móvil_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>1</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="14.4" customHeight="1">
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CRT26-019265</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>12283</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>NEGOCIOS INTEGRALES DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>MIGUEL ENRIQUE LIZARRAGA JIMENEZ</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>06/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>519992_negocios_integrales_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>1</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="14.4" customHeight="1">
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CRT26-019259</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>12282</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>BENE LEIT, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>DANIEL ESCUDERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>06/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>519996_bene_leit_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>1</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="14.4" customHeight="1">
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CRT26-019254</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>174971</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>MININET, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>HERNÁN ANTONIO GONZÁLEZ BAQUEIRO</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>520120_mininet_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="14.4" customHeight="1">
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CRT26-019253</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>174970</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>MININET, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>HERNÁN ANTONIO GONZÁLEZ BAQUEIRO</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>520120_mininet_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="14.4" customHeight="1">
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CRT26-019243</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>174963</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>EURONET TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>521054_euronet_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="14.4" customHeight="1">
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CRT26-019194</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>174873</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>VÍCTOR SANTOS SERRANO</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>VÍCTOR SANTOS SERRANO</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>518898_víctor_santos_serrano\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="14.4" customHeight="1">
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CRT26-019193</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>174872</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>VÍCTOR SANTOS SERRANO</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>VÍCTOR SANTOS SERRANO</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>518898_víctor_santos_serrano\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="14.4" customHeight="1">
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CRT26-019182</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>174861</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>EURONET TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>521054_euronet_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="14.4" customHeight="1">
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CRT26-019168</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>174853</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>EURONET TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>521054_euronet_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="14.4" customHeight="1">
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CRT26-019136</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>12189</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>YONATHAN CITALAN MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>YONATHAN CITALAN MARTINEZ</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>05/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>526019_yonathan_citalan_martinez\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="14.4" customHeight="1">
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CRT26-019066</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>174740</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>ALTÁN REDES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>CARLOS JUAN DE DIOS SANCHEZ BRETON</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>510310_altán_redes_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="14.4" customHeight="1">
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CRT26-019061</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>174733</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ALTÁN REDES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>CARLOS JUAN DE DIOS SANCHEZ BRETON</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>510310_altán_redes_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="14.4" customHeight="1">
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CRT26-019058</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>174731</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ALTÁN REDES, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>CARLOS JUAN DE DIOS SANCHEZ BRETON</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>510310_altán_redes_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
         </is>
       </c>
     </row>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR205"/>
+  <dimension ref="A1:AR240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -8327,6 +8327,1429 @@
       <c r="AO205" t="inlineStr">
         <is>
           <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>15/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>1</v>
+      </c>
+      <c r="S213" t="n">
+        <v>1</v>
+      </c>
+      <c r="X213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>15/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>1</v>
+      </c>
+      <c r="S224" t="n">
+        <v>1</v>
+      </c>
+      <c r="X224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>CRT26-027529</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>184737</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>15/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>1</v>
+      </c>
+      <c r="S233" t="n">
+        <v>1</v>
+      </c>
+      <c r="X233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>15/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>1</v>
+      </c>
+      <c r="S239" t="n">
+        <v>1</v>
+      </c>
+      <c r="X239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
         </is>
       </c>
     </row>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR240"/>
+  <dimension ref="A1:AR260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -9748,6 +9748,788 @@
         <v>1</v>
       </c>
       <c r="AO240" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CRT26-027529</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>184737</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>CRT26-027529</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>184737</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>CRT26-027529</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>184737</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>CRT26-027529</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>184737</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>ALLCER INNOVACIÓN Y TECNOLOGÍA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>SERGIO ALLARD GAXIOLA</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>521679_allcer_innovación_y_tecnología_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>CRT26-027529</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>184737</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>ALLCER INNOVACIÓN Y TECNOLOGÍA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>SERGIO ALLARD GAXIOLA</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>521679_allcer_innovación_y_tecnología_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>CRT26-027529</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>184737</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ALLCER INNOVACIÓN Y TECNOLOGÍA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>SERGIO ALLARD GAXIOLA</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>521679_allcer_innovación_y_tecnología_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO260" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
         </is>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR260"/>
+  <dimension ref="A1:AR265"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -10530,6 +10530,203 @@
         <v>1</v>
       </c>
       <c r="AO260" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CRT26-013461</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>166095</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>HISPASAT MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>GUILLERMO SANTOS MAZA MONCADA</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>100678_hispasat_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CRT26-027740</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>184911</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="O263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CRT26-027529</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>184737</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AL264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>ALLCER INNOVACIÓN Y TECNOLOGÍA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>SERGIO ALLARD GAXIOLA</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>521679_allcer_innovación_y_tecnología_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO265" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
         </is>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR265"/>
+  <dimension ref="A1:AR307"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -10727,6 +10727,1608 @@
         <v>1</v>
       </c>
       <c r="AO265" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>CRT26-027904</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>CRT26-027904</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>ALESTRA SERVICIOS MOVILES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>SAMANTA PAOLA LEMUS NIETO</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>02/07/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>CRT26-027908</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>CRT26-027908</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>02/07/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CRT26-027890</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>CRT26-027890</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>NORMA GLEZZ</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>NORMA GLEZZ</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>01/07/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>CRT26-027838</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>CRT26-027838</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>NORMA GLEZZ</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>NORMA GLEZZ</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>01/07/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>CRT26-027836</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>184980</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>IENTC, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>106870_ientc_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CRT26-027739</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>CRT26-027739</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ROGELIO CASTILLO ROSALES</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>ROGELIO CASTILLO ROSALES</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>01/07/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>CRT26-027738</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>CRT26-027738</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>CARLA MARIANA CELIS MEDINA</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>CARLA MARIANA CELIS MEDINA</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>01/07/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CRT26-027727</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>184901</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>MEGABIT TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OSCAR ORTEGA FLORES</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>519381_megabit_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CRT26-027663</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>184820</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>CALLPICKER, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>JOSÉ ANTONIO DEL RÍO GARIBAY</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>521980_callpicker_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>CRT26-027632</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>CRT26-027632</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>OMAR ALONSO RODRIGUEZ NAVARRO</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OMAR ALONSO RODRIGUEZ NAVARRO</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>30/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>CRT26-027559</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>CRT26-027559</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>RICARDO TORRES.</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>RICARDO TORRES.</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>30/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CRT26-027628</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>CRT26-027628</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>FLORENCIO ROMAN CRUZ SATA ANNA</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>FLORENCIO ROMAN CRUZ SANTA ANNA</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>30/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>CRT26-027626</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>CRT26-027626</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>RICARDO PACHECO</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>RICARDO PACHECO</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>30/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>CRT26-027532</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>184741</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CRT26-027525</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>184733</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CRT26-027468</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>184700</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>IENTC, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>106870_ientc_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>CRT26-027906</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>185035</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>EURONET TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>521054_euronet_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>CRT26-027538</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>184744</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>JESÚS ANAHÍ MARTÍNEZ GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>521754_jesús_anahí_martínez_gonzález\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CRT26-027462</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>184698</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>IENTC, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>106870_ientc_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>ALLCER INNOVACIÓN Y TECNOLOGÍA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>SERGIO ALLARD GAXIOLA</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>521679_allcer_innovación_y_tecnología_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>15/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>1</v>
+      </c>
+      <c r="S290" t="n">
+        <v>1</v>
+      </c>
+      <c r="X290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO297" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO299" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>15/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>1</v>
+      </c>
+      <c r="S300" t="n">
+        <v>1</v>
+      </c>
+      <c r="X300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO300" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO301" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO302" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO303" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO304" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO305" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>1</v>
+      </c>
+      <c r="S306" t="n">
+        <v>1</v>
+      </c>
+      <c r="X306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO306" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO307" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
         </is>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR307"/>
+  <dimension ref="A1:AR322"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="10.77734375" customWidth="1" min="1" max="3"/>
@@ -12331,6 +12331,614 @@
       <c r="AO307" t="inlineStr">
         <is>
           <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO308" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>CRT26-021820</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>178113</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>CMC SERVICE NETWORK, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA CABALLERO BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>520983_cmc_service_network_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO309" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>CRT26-021815</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>178112</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>COMUNÍCALO DE MÉXICO, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>JOSÉ LUIS CARRILLO SALAS</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>106476_comunícalo_de_méxico_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO310" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>CRT26-021732</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>178065</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>TELEVERA RED, S.A.P.I. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA AGUIRRE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>105790_televera_red_s_a_p_i_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO311" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>CRT26-020606</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>PEGASO PCS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ANGELA NATALIA ANDREA FEDERICA GUERRA CAICEDO</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>15/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>101346_pegaso_pcs_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>1</v>
+      </c>
+      <c r="S312" t="n">
+        <v>1</v>
+      </c>
+      <c r="X312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO312" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>CRT26-002483</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>CABLE RED ACUÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>DANIELA GARCIA NOCETTI</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>21/01/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="W313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>CRT26-027462</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>184698</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>IENTC, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>106870_ientc_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json, .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>ALLCER INNOVACIÓN Y TECNOLOGÍA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>SERGIO ALLARD GAXIOLA</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>521679_allcer_innovación_y_tecnología_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>Formato entregado en .json</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>CRT26-027462</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>184698</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>IENTC, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>LA PRESENTE ENTREGA SE REALIZA DE FORMA EXTEMPORANEA Y VOLUNTARIA SIN QUE MEDIE REQUERIMIENTO DE AUTORIDAD.</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>CGPE-01-003-L: Entrega periódica de Información General Estadística L. Sobre el Servicio Minorista Móvil de Acceso a Internet bajo esquema OMV</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>106870_ientc_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>Formato entregado en .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>8529</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>ALLCER INNOVACIÓN Y TECNOLOGÍA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>SERGIO ALLARD GAXIOLA</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>FORMATO R025</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>521679_allcer_innovación_y_tecnología_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>PRESENTA QUEJA POR LA VINCULACION DE SU LINEA TELEFONICA POR PARTE DE LA EMPRESA AT&amp;T. (Se recibió vía correo electrónico oficialiadepartes@crt.gob.mx) (04:43 p. m.) (AC)</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CRT26-027462</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>184698</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>IENTC, S. DE R.L. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO SÁNCHEZ ASSAD</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>LA PRESENTE ENTREGA SE REALIZA DE FORMA EXTEMPORANEA Y VOLUNTARIA SIN QUE MEDIE REQUERIMIENTO DE AUTORIDAD.</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>CGPE-01-003-L: Entrega periódica de Información General Estadística L. Sobre el Servicio Minorista Móvil de Acceso a Internet bajo esquema OMV</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>106870_ientc_s_de_r_l_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>Formato entregado en .xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>CRT26-011878</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>8529</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>ALLCER INNOVACIÓN Y TECNOLOGÍA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>SERGIO ALLARD GAXIOLA</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>FORMATO R025</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>521679_allcer_innovación_y_tecnología_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AN321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>CRT26-025610</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>JUANA RAMOS MONTIEL</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>PRESENTA QUEJA POR LA VINCULACION DE SU LINEA TELEFONICA POR PARTE DE LA EMPRESA AT&amp;T. (Se recibió vía correo electrónico oficialiadepartes@crt.gob.mx) (04:43 p. m.) (AC)</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00:00</t>
         </is>
       </c>
     </row>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -78224,7 +78224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.77734375" customWidth="1" min="1" max="1"/>
@@ -78702,6 +78702,105 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>107831</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>107831</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DIRI TELECOMUNICACIONES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ALEJANDRO CORSI AMERLINCK</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CGPE-01-003: ENTREGA PERIODICA DE INFORMACION GENERAL ESTADISTICA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>06/03/2025</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>517649_diri_telecomunicaciones_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Formato entregado en .xlsx</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>107831</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>145494</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>145494</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MEGA CABLE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SERGIO DANILO PANCARDO COBOS</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CGPE-01-003: ENTREGA PERIODICA DE INFORMACION GENERAL ESTADISTICA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>100418_mega_cable_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>145494</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TrámitesCRT.xlsx
+++ b/TrámitesCRT.xlsx
@@ -78224,7 +78224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS7"/>
+  <dimension ref="A1:AS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.77734375" customWidth="1" min="1" max="1"/>
@@ -78801,6 +78801,58 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>146178</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>146178</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>APCO NETWORKS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CARLOS ARTURO BELLO HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CGPE-01-004: Solicitud de rectificación de información para integrar el acervo estadístico del sector de telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>11/01/2026</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>100477_apco_networks_s_a_de_c_v\01 EN\VE</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Formato entregado en .xlsx</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>146178</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
